--- a/research/traditional_assets/database/data/turkey/turkey_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.442</v>
-      </c>
-      <c r="F2">
-        <v>0.08</v>
+        <v>0.5329999999999999</v>
+      </c>
+      <c r="E2">
+        <v>1.069</v>
       </c>
       <c r="G2">
-        <v>0.3252242926155969</v>
+        <v>0.2023107757604339</v>
       </c>
       <c r="H2">
-        <v>0.3252242926155969</v>
+        <v>0.2023107757604339</v>
       </c>
       <c r="I2">
-        <v>0.2481021394064872</v>
+        <v>0.07144541381749588</v>
       </c>
       <c r="J2">
-        <v>0.1878296815829732</v>
+        <v>0.06090585181731948</v>
       </c>
       <c r="K2">
-        <v>112.5</v>
+        <v>44.7</v>
       </c>
       <c r="L2">
-        <v>0.1940993788819876</v>
+        <v>0.1053996698891771</v>
       </c>
       <c r="M2">
-        <v>118.6</v>
+        <v>28.6</v>
       </c>
       <c r="N2">
-        <v>0.2674785746504285</v>
+        <v>0.03680350019302535</v>
       </c>
       <c r="O2">
-        <v>1.054222222222222</v>
+        <v>0.6398210290827741</v>
       </c>
       <c r="P2">
-        <v>118.6</v>
+        <v>28.6</v>
       </c>
       <c r="Q2">
-        <v>0.2674785746504285</v>
+        <v>0.03680350019302535</v>
       </c>
       <c r="R2">
-        <v>1.054222222222222</v>
+        <v>0.6398210290827741</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,46 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>569.8</v>
+        <v>269.5</v>
       </c>
       <c r="V2">
-        <v>1.285069914298602</v>
+        <v>0.3468022133573543</v>
       </c>
       <c r="W2">
-        <v>0.27620918242082</v>
+        <v>0.1024524409809764</v>
       </c>
       <c r="X2">
-        <v>0.08309298539461134</v>
+        <v>0.1438204774443744</v>
       </c>
       <c r="Y2">
-        <v>0.1931161970262087</v>
-      </c>
-      <c r="Z2">
-        <v>-2.352654651729177</v>
-      </c>
-      <c r="AA2">
-        <v>-0.4418983741089919</v>
+        <v>-0.04136803646339797</v>
       </c>
       <c r="AB2">
-        <v>0.08300570018069096</v>
-      </c>
-      <c r="AC2">
-        <v>-0.5249040742896829</v>
+        <v>0.1437336798009936</v>
       </c>
       <c r="AD2">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG2">
-        <v>-568.13</v>
+        <v>-267.82</v>
       </c>
       <c r="AH2">
-        <v>0.00375221875210641</v>
+        <v>0.002157220267598038</v>
       </c>
       <c r="AI2">
-        <v>0.003813046555700162</v>
+        <v>0.007032819825853985</v>
       </c>
       <c r="AJ2">
-        <v>4.554878537641304</v>
+        <v>-0.5258796732642161</v>
       </c>
       <c r="AK2">
-        <v>4.309565349313511</v>
+        <v>8.746570868713258</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.01139154160982265</v>
+        <v>0.05217391304347825</v>
       </c>
       <c r="AP2">
-        <v>-3.87537517053206</v>
+        <v>-8.317391304347826</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +707,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.442</v>
-      </c>
-      <c r="F3">
-        <v>0.08</v>
+        <v>0.5329999999999999</v>
+      </c>
+      <c r="E3">
+        <v>1.069</v>
       </c>
       <c r="G3">
-        <v>0.3252242926155969</v>
+        <v>0.2023107757604339</v>
       </c>
       <c r="H3">
-        <v>0.3252242926155969</v>
+        <v>0.2023107757604339</v>
       </c>
       <c r="I3">
-        <v>0.2481021394064872</v>
+        <v>0.07144541381749588</v>
       </c>
       <c r="J3">
-        <v>0.1878296815829732</v>
+        <v>0.06090585181731948</v>
       </c>
       <c r="K3">
-        <v>112.5</v>
+        <v>44.7</v>
       </c>
       <c r="L3">
-        <v>0.1940993788819876</v>
+        <v>0.1053996698891771</v>
       </c>
       <c r="M3">
-        <v>118.6</v>
+        <v>28.6</v>
       </c>
       <c r="N3">
-        <v>0.2674785746504285</v>
+        <v>0.03680350019302535</v>
       </c>
       <c r="O3">
-        <v>1.054222222222222</v>
+        <v>0.6398210290827741</v>
       </c>
       <c r="P3">
-        <v>118.6</v>
+        <v>28.6</v>
       </c>
       <c r="Q3">
-        <v>0.2674785746504285</v>
+        <v>0.03680350019302535</v>
       </c>
       <c r="R3">
-        <v>1.054222222222222</v>
+        <v>0.6398210290827741</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +755,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>569.8</v>
+        <v>269.5</v>
       </c>
       <c r="V3">
-        <v>1.285069914298602</v>
+        <v>0.3468022133573543</v>
       </c>
       <c r="W3">
-        <v>0.27620918242082</v>
+        <v>0.1024524409809764</v>
       </c>
       <c r="X3">
-        <v>0.08309298539461134</v>
+        <v>0.1438204774443744</v>
       </c>
       <c r="Y3">
-        <v>0.1931161970262087</v>
-      </c>
-      <c r="Z3">
-        <v>-2.352654651729177</v>
-      </c>
-      <c r="AA3">
-        <v>-0.4418983741089919</v>
+        <v>-0.04136803646339797</v>
       </c>
       <c r="AB3">
-        <v>0.08300570018069096</v>
-      </c>
-      <c r="AC3">
-        <v>-0.5249040742896829</v>
+        <v>0.1437336798009936</v>
       </c>
       <c r="AD3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG3">
-        <v>-568.13</v>
+        <v>-267.82</v>
       </c>
       <c r="AH3">
-        <v>0.00375221875210641</v>
+        <v>0.002157220267598038</v>
       </c>
       <c r="AI3">
-        <v>0.003813046555700162</v>
+        <v>0.007032819825853985</v>
       </c>
       <c r="AJ3">
-        <v>4.554878537641304</v>
+        <v>-0.5258796732642161</v>
       </c>
       <c r="AK3">
-        <v>4.309565349313511</v>
+        <v>8.746570868713258</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.01139154160982265</v>
+        <v>0.05217391304347825</v>
       </c>
       <c r="AP3">
-        <v>-3.87537517053206</v>
+        <v>-8.317391304347826</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/turkey/turkey_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.5329999999999999</v>
+        <v>0.8490000000000001</v>
       </c>
       <c r="E2">
-        <v>1.069</v>
+        <v>1.596</v>
       </c>
       <c r="G2">
-        <v>0.2023107757604339</v>
+        <v>0.05249879865449304</v>
       </c>
       <c r="H2">
-        <v>0.2023107757604339</v>
+        <v>0.05249879865449304</v>
       </c>
       <c r="I2">
-        <v>0.07144541381749588</v>
+        <v>0.2415905814512254</v>
       </c>
       <c r="J2">
-        <v>0.06090585181731948</v>
+        <v>0.1967583412861282</v>
       </c>
       <c r="K2">
-        <v>44.7</v>
+        <v>203.2</v>
       </c>
       <c r="L2">
-        <v>0.1053996698891771</v>
+        <v>0.2441134070158578</v>
       </c>
       <c r="M2">
-        <v>28.6</v>
+        <v>5.67</v>
       </c>
       <c r="N2">
-        <v>0.03680350019302535</v>
+        <v>0.00355909861276756</v>
       </c>
       <c r="O2">
-        <v>0.6398210290827741</v>
+        <v>0.02790354330708662</v>
       </c>
       <c r="P2">
-        <v>28.6</v>
+        <v>5.67</v>
       </c>
       <c r="Q2">
-        <v>0.03680350019302535</v>
+        <v>0.00355909861276756</v>
       </c>
       <c r="R2">
-        <v>0.6398210290827741</v>
+        <v>0.02790354330708662</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,46 +636,46 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>269.5</v>
+        <v>786</v>
       </c>
       <c r="V2">
-        <v>0.3468022133573543</v>
+        <v>0.4933776912937041</v>
       </c>
       <c r="W2">
-        <v>0.1024524409809764</v>
+        <v>0.8566610455311973</v>
       </c>
       <c r="X2">
-        <v>0.1438204774443744</v>
+        <v>0.1522738925562448</v>
       </c>
       <c r="Y2">
-        <v>-0.04136803646339797</v>
+        <v>0.7043871529749525</v>
       </c>
       <c r="AB2">
-        <v>0.1437336798009936</v>
+        <v>0.1351575847871791</v>
       </c>
       <c r="AD2">
-        <v>1.68</v>
+        <v>621</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.68</v>
+        <v>621</v>
       </c>
       <c r="AG2">
-        <v>-267.82</v>
+        <v>-165</v>
       </c>
       <c r="AH2">
-        <v>0.002157220267598038</v>
+        <v>0.2804751366243621</v>
       </c>
       <c r="AI2">
-        <v>0.007032819825853985</v>
+        <v>0.5944290226859386</v>
       </c>
       <c r="AJ2">
-        <v>-0.5258796732642161</v>
+        <v>-0.1155381275821021</v>
       </c>
       <c r="AK2">
-        <v>8.746570868713258</v>
+        <v>-0.6378044066486278</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -684,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.05217391304347825</v>
+        <v>3.056102362204725</v>
       </c>
       <c r="AP2">
-        <v>-8.317391304347826</v>
+        <v>-0.812007874015748</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +698,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Türkiye Sigorta Anonim Sirketi (IBSE:TURSG)</t>
+          <t>Türkiye Sigorta A.S. (IBSE:TURSG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -707,46 +707,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.5329999999999999</v>
+        <v>0.8490000000000001</v>
       </c>
       <c r="E3">
-        <v>1.069</v>
+        <v>1.596</v>
       </c>
       <c r="G3">
-        <v>0.2023107757604339</v>
+        <v>0.05249879865449304</v>
       </c>
       <c r="H3">
-        <v>0.2023107757604339</v>
+        <v>0.05249879865449304</v>
       </c>
       <c r="I3">
-        <v>0.07144541381749588</v>
+        <v>0.2415905814512254</v>
       </c>
       <c r="J3">
-        <v>0.06090585181731948</v>
+        <v>0.1967583412861282</v>
       </c>
       <c r="K3">
-        <v>44.7</v>
+        <v>203.2</v>
       </c>
       <c r="L3">
-        <v>0.1053996698891771</v>
+        <v>0.2441134070158578</v>
       </c>
       <c r="M3">
-        <v>28.6</v>
+        <v>5.67</v>
       </c>
       <c r="N3">
-        <v>0.03680350019302535</v>
+        <v>0.00355909861276756</v>
       </c>
       <c r="O3">
-        <v>0.6398210290827741</v>
+        <v>0.02790354330708662</v>
       </c>
       <c r="P3">
-        <v>28.6</v>
+        <v>5.67</v>
       </c>
       <c r="Q3">
-        <v>0.03680350019302535</v>
+        <v>0.00355909861276756</v>
       </c>
       <c r="R3">
-        <v>0.6398210290827741</v>
+        <v>0.02790354330708662</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -755,46 +755,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>269.5</v>
+        <v>786</v>
       </c>
       <c r="V3">
-        <v>0.3468022133573543</v>
+        <v>0.4933776912937041</v>
       </c>
       <c r="W3">
-        <v>0.1024524409809764</v>
+        <v>0.8566610455311973</v>
       </c>
       <c r="X3">
-        <v>0.1438204774443744</v>
+        <v>0.1522738925562448</v>
       </c>
       <c r="Y3">
-        <v>-0.04136803646339797</v>
+        <v>0.7043871529749525</v>
       </c>
       <c r="AB3">
-        <v>0.1437336798009936</v>
+        <v>0.1351575847871791</v>
       </c>
       <c r="AD3">
-        <v>1.68</v>
+        <v>621</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.68</v>
+        <v>621</v>
       </c>
       <c r="AG3">
-        <v>-267.82</v>
+        <v>-165</v>
       </c>
       <c r="AH3">
-        <v>0.002157220267598038</v>
+        <v>0.2804751366243621</v>
       </c>
       <c r="AI3">
-        <v>0.007032819825853985</v>
+        <v>0.5944290226859386</v>
       </c>
       <c r="AJ3">
-        <v>-0.5258796732642161</v>
+        <v>-0.1155381275821021</v>
       </c>
       <c r="AK3">
-        <v>8.746570868713258</v>
+        <v>-0.6378044066486278</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -803,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.05217391304347825</v>
+        <v>3.056102362204725</v>
       </c>
       <c r="AP3">
-        <v>-8.317391304347826</v>
+        <v>-0.812007874015748</v>
       </c>
     </row>
   </sheetData>
